--- a/artfynd/A 42138-2021 artfynd.xlsx
+++ b/artfynd/A 42138-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42138-2021 artfynd.xlsx
+++ b/artfynd/A 42138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66544599</v>
+        <v>104314163</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ammarnäs N, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554840.1155808475</v>
+        <v>555053</v>
       </c>
       <c r="R2" t="n">
-        <v>7318972.782483704</v>
+        <v>7318647</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>25325</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104314149</v>
+        <v>104796975</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,47 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Norra Ammarnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554884.3373764047</v>
+        <v>554914</v>
       </c>
       <c r="R3" t="n">
-        <v>7318562.376520898</v>
+        <v>7318769</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,65 +862,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104796968</v>
+        <v>66544599</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Ammarnäs, Ly lm</t>
+          <t>Ammarnäs N, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555046.0493613532</v>
+        <v>554840</v>
       </c>
       <c r="R4" t="n">
-        <v>7318746.474542381</v>
+        <v>7318973</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,53 +955,53 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>25325</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104796978</v>
+        <v>104796974</v>
       </c>
       <c r="B5" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554910.7824624187</v>
+        <v>555020</v>
       </c>
       <c r="R5" t="n">
-        <v>7318820.489835358</v>
+        <v>7318828</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1099,19 +1044,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,37 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104796982</v>
+        <v>104796967</v>
       </c>
       <c r="B6" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555044.0098800426</v>
+        <v>555020</v>
       </c>
       <c r="R6" t="n">
-        <v>7318746.435124381</v>
+        <v>7318757</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1211,19 +1141,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104796981</v>
+        <v>104796978</v>
       </c>
       <c r="B7" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555044.8256725698</v>
+        <v>554911</v>
       </c>
       <c r="R7" t="n">
-        <v>7318746.450891404</v>
+        <v>7318821</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1323,19 +1238,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,37 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104796977</v>
+        <v>104796983</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554859.5130271561</v>
+        <v>555068</v>
       </c>
       <c r="R8" t="n">
-        <v>7318940.143528248</v>
+        <v>7318737</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1435,19 +1335,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,37 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104796974</v>
+        <v>104796970</v>
       </c>
       <c r="B9" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555019.9934400739</v>
+        <v>555020</v>
       </c>
       <c r="R9" t="n">
-        <v>7318827.896188599</v>
+        <v>7318828</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1547,19 +1432,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104796972</v>
+        <v>104796971</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555029.0786030027</v>
+        <v>555022</v>
       </c>
       <c r="R10" t="n">
-        <v>7318801.171190139</v>
+        <v>7318826</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,19 +1529,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,37 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104796967</v>
+        <v>104796972</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555019.7314762429</v>
+        <v>555029</v>
       </c>
       <c r="R11" t="n">
-        <v>7318756.97100158</v>
+        <v>7318801</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1771,19 +1626,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104796980</v>
+        <v>104796973</v>
       </c>
       <c r="B12" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554871.9456688522</v>
+        <v>555005</v>
       </c>
       <c r="R12" t="n">
-        <v>7318909.00038479</v>
+        <v>7318828</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1883,19 +1723,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,15 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104796970</v>
+        <v>104796980</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555019.9934400739</v>
+        <v>554872</v>
       </c>
       <c r="R13" t="n">
-        <v>7318827.896188599</v>
+        <v>7318909</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1995,19 +1820,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,37 +1849,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104796983</v>
+        <v>104796968</v>
       </c>
       <c r="B14" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555067.8648133522</v>
+        <v>555046</v>
       </c>
       <c r="R14" t="n">
-        <v>7318736.70640995</v>
+        <v>7318746</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2107,19 +1917,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,15 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104796971</v>
+        <v>104796982</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555022.0722208177</v>
+        <v>555044</v>
       </c>
       <c r="R15" t="n">
-        <v>7318825.898439893</v>
+        <v>7318747</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2219,19 +2014,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,37 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104796975</v>
+        <v>104796981</v>
       </c>
       <c r="B16" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554913.8196014973</v>
+        <v>555045</v>
       </c>
       <c r="R16" t="n">
-        <v>7318768.784977633</v>
+        <v>7318746</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2331,19 +2111,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,15 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104796973</v>
+        <v>66544600</v>
       </c>
       <c r="B17" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2386,37 +2151,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norra Ammarnäs, Ly lm</t>
+          <t>Ammarnäs N, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555004.8938407352</v>
+        <v>554840</v>
       </c>
       <c r="R17" t="n">
-        <v>7318828.012096215</v>
+        <v>7318973</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,22 +2205,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,69 +2221,79 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>25326</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104796976</v>
+        <v>104314149</v>
       </c>
       <c r="B18" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Ammarnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554959.5626364228</v>
+        <v>554884</v>
       </c>
       <c r="R18" t="n">
-        <v>7318851.184142754</v>
+        <v>7318563</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2552,22 +2317,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,15 +2337,209 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104796976</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norra Ammarnäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>554959</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7318851</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104796977</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norra Ammarnäs, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>554860</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7318940</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42138-2021 artfynd.xlsx
+++ b/artfynd/A 42138-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104314163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796975</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796974</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796983</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796970</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796971</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796972</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796973</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796980</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796968</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796982</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796981</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66544600</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104314149</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796976</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,8 +2635,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104796977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>